--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="quest_data" sheetId="1" r:id="rId1"/>
+    <sheet name="quest_step_data" sheetId="2" r:id="rId2"/>
+    <sheet name="quest_step_outcome" sheetId="4" r:id="rId3"/>
+    <sheet name="quest_step_objective" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,72 +30,238 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
+    <t>id</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>init_step_id</t>
+  </si>
+  <si>
+    <t>finish_reward</t>
+  </si>
+  <si>
+    <t>is_auto_accept</t>
+  </si>
+  <si>
+    <t>acceept_cond</t>
+  </si>
+  <si>
+    <t>start_npc_id</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(map#sep=,|),string,int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>demo.EQuestProgressType</t>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>初始step</t>
+  </si>
+  <si>
+    <t>完成奖励</t>
+  </si>
+  <si>
+    <t>是否自动接取</t>
+  </si>
+  <si>
+    <t>解锁条件</t>
+  </si>
+  <si>
+    <t>接取npcid</t>
+  </si>
+  <si>
+    <t>初始任务</t>
+  </si>
+  <si>
+    <t>100_01</t>
+  </si>
+  <si>
+    <t>gold,10|bundle_01,20</t>
+  </si>
+  <si>
+    <t>初始任务2</t>
+  </si>
+  <si>
+    <t>101_01</t>
+  </si>
+  <si>
+    <t>TaskFinish,100,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>初始任务3</t>
+  </si>
+  <si>
+    <t>102_01</t>
+  </si>
+  <si>
+    <t>TaskFinish,101,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>quest_id</t>
+  </si>
+  <si>
+    <t>is_root</t>
+  </si>
+  <si>
+    <t>auto_next</t>
+  </si>
+  <si>
+    <t>push_npc_id</t>
+  </si>
+  <si>
+    <t>objectives</t>
+  </si>
+  <si>
+    <t>outcomes</t>
+  </si>
+  <si>
+    <t>(list#sep=;),string</t>
+  </si>
+  <si>
+    <t>所属任务</t>
+  </si>
+  <si>
+    <t>是否是根</t>
+  </si>
+  <si>
+    <t>是否自动</t>
+  </si>
+  <si>
+    <t>推进npc</t>
+  </si>
+  <si>
+    <t>目标列表
+每个目标对应一个进度统计项</t>
+  </si>
+  <si>
+    <t>出口列表</t>
+  </si>
+  <si>
+    <t>100_02</t>
+  </si>
+  <si>
+    <t>need_objective_ids</t>
+  </si>
+  <si>
+    <t>next_step_id</t>
+  </si>
+  <si>
+    <t>所需目标</t>
+  </si>
+  <si>
+    <t>下一步</t>
+  </si>
+  <si>
+    <t>format_desc</t>
+  </si>
+  <si>
+    <t>is_option</t>
+  </si>
+  <si>
+    <t>is_hidden</t>
+  </si>
+  <si>
+    <t>completion_tag</t>
+  </si>
+  <si>
+    <t>progress_type</t>
+  </si>
+  <si>
+    <t>progress_target</t>
+  </si>
+  <si>
+    <t>progress_param_int1</t>
+  </si>
+  <si>
+    <t>progress_param_int2</t>
+  </si>
+  <si>
+    <t>progress_param_str1</t>
+  </si>
+  <si>
+    <t>progress_param_complex</t>
+  </si>
+  <si>
+    <t>EQuestProgressType</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>格式化描述</t>
+  </si>
+  <si>
+    <t>是否隐藏</t>
+  </si>
+  <si>
+    <t>完成标记</t>
+  </si>
+  <si>
+    <t>进度类型</t>
+  </si>
+  <si>
+    <t>进度要求</t>
+  </si>
+  <si>
+    <t>进度参数1
+int</t>
+  </si>
+  <si>
+    <t>进度参数2
+int</t>
+  </si>
+  <si>
+    <t>进度参数1
+str</t>
+  </si>
+  <si>
+    <t>复杂进度参数</t>
+  </si>
+  <si>
+    <t>obj_100_s1_01</t>
   </si>
   <si>
     <t>KillMonster</t>
-  </si>
-  <si>
-    <t>OwnItem</t>
   </si>
 </sst>
 </file>
@@ -260,7 +427,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +436,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -460,27 +621,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -607,7 +753,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -619,133 +765,127 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1058,15 +1198,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="25.125" customWidth="1"/>
     <col min="3" max="6" width="33.125" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
+    <col min="7" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,96 +1227,181 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="40.5" spans="1:12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
       <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="1">
+        <v>100</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1">
+        <v>101</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="1">
+        <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1184,9 +1411,174 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <cols>
+    <col min="6" max="7" width="16.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="40.5" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>100</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="1">
+        <v>100</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>101</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>102</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1196,11 +1588,311 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="4" width="29.625" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="8" max="8" width="9.75" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="11" width="14.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
@@ -30,65 +30,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>quest_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>init_step_id</t>
+  </si>
+  <si>
+    <t>finish_reward</t>
+  </si>
+  <si>
+    <t>is_auto_accept</t>
+  </si>
+  <si>
+    <t>acceept_cond</t>
+  </si>
+  <si>
+    <t>start_npc_id</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(map#sep=,|),string,int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>init_step_id</t>
-  </si>
-  <si>
-    <t>finish_reward</t>
-  </si>
-  <si>
-    <t>is_auto_accept</t>
-  </si>
-  <si>
-    <t>acceept_cond</t>
-  </si>
-  <si>
-    <t>start_npc_id</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(map#sep=,|),string,int</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>(list#sep=;),CommonCheckCond</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
@@ -137,7 +140,7 @@
     <t>TaskFinish,101,0,0,0,0,0</t>
   </si>
   <si>
-    <t>quest_id</t>
+    <t>step_id</t>
   </si>
   <si>
     <t>is_root</t>
@@ -177,21 +180,60 @@
     <t>出口列表</t>
   </si>
   <si>
-    <t>100_02</t>
+    <t>100_s1</t>
+  </si>
+  <si>
+    <t>击杀刷新怪物</t>
+  </si>
+  <si>
+    <t>100_s1_Main</t>
+  </si>
+  <si>
+    <t>100_s2</t>
+  </si>
+  <si>
+    <t>击杀刷新头目</t>
+  </si>
+  <si>
+    <t>100_s2_Main</t>
+  </si>
+  <si>
+    <t>outcome_id</t>
   </si>
   <si>
     <t>need_objective_ids</t>
   </si>
   <si>
+    <t>is_final</t>
+  </si>
+  <si>
+    <t>is_fail</t>
+  </si>
+  <si>
     <t>next_step_id</t>
   </si>
   <si>
     <t>所需目标</t>
   </si>
   <si>
+    <t>是否是最后一步</t>
+  </si>
+  <si>
+    <t>是否是失败</t>
+  </si>
+  <si>
     <t>下一步</t>
   </si>
   <si>
+    <t>100 s1 主跳转</t>
+  </si>
+  <si>
+    <t>100 s2 主跳转</t>
+  </si>
+  <si>
+    <t>obj_id</t>
+  </si>
+  <si>
     <t>format_desc</t>
   </si>
   <si>
@@ -204,25 +246,34 @@
     <t>completion_tag</t>
   </si>
   <si>
-    <t>progress_type</t>
-  </si>
-  <si>
-    <t>progress_target</t>
-  </si>
-  <si>
-    <t>progress_param_int1</t>
-  </si>
-  <si>
-    <t>progress_param_int2</t>
-  </si>
-  <si>
-    <t>progress_param_str1</t>
-  </si>
-  <si>
-    <t>progress_param_complex</t>
-  </si>
-  <si>
-    <t>EQuestProgressType</t>
+    <t>obj_type</t>
+  </si>
+  <si>
+    <t>obj_progress</t>
+  </si>
+  <si>
+    <t>obj_p0</t>
+  </si>
+  <si>
+    <t>obj_p1</t>
+  </si>
+  <si>
+    <t>obj_p2</t>
+  </si>
+  <si>
+    <t>obj_p3</t>
+  </si>
+  <si>
+    <t>obj_p4</t>
+  </si>
+  <si>
+    <t>obj_p5</t>
+  </si>
+  <si>
+    <t>obj_p_extra</t>
+  </si>
+  <si>
+    <t>EQuestObjectiveType</t>
   </si>
   <si>
     <t>long</t>
@@ -237,31 +288,49 @@
     <t>完成标记</t>
   </si>
   <si>
-    <t>进度类型</t>
+    <t>目标类型</t>
   </si>
   <si>
     <t>进度要求</t>
   </si>
   <si>
-    <t>进度参数1
+    <t>p0
 int</t>
   </si>
   <si>
-    <t>进度参数2
+    <t>p1
 int</t>
   </si>
   <si>
-    <t>进度参数1
-str</t>
+    <t>p2
+long</t>
+  </si>
+  <si>
+    <t>p3
+long</t>
+  </si>
+  <si>
+    <t>p4
+long</t>
+  </si>
+  <si>
+    <t>p5
+long</t>
   </si>
   <si>
     <t>复杂进度参数</t>
   </si>
   <si>
-    <t>obj_100_s1_01</t>
+    <t>击杀XX</t>
   </si>
   <si>
     <t>KillMonster</t>
+  </si>
+  <si>
+    <t>initial_orc_01</t>
+  </si>
+  <si>
+    <t>initial_orc_02</t>
   </si>
 </sst>
 </file>
@@ -1307,29 +1376,29 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1337,17 +1406,17 @@
         <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -1358,23 +1427,23 @@
         <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1382,23 +1451,23 @@
         <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1411,24 +1480,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="6" max="7" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="33.875" customWidth="1"/>
+    <col min="7" max="8" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>36</v>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E1" t="s">
         <v>37</v>
@@ -1442,8 +1512,11 @@
       <c r="H1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1453,23 +1526,26 @@
       <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
       <c r="H2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1494,19 +1570,22 @@
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="40.5" spans="1:8">
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="40.5" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" t="s">
         <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E4" t="s">
         <v>44</v>
@@ -1514,68 +1593,102 @@
       <c r="F4" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1">
         <v>100</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1">
         <v>100</v>
       </c>
-      <c r="E6" t="b">
+      <c r="D6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>101</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>102</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
       <c r="E9" t="b">
         <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1588,32 +1701,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="25.625" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20.375" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1622,13 +1746,22 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1642,44 +1775,89 @@
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C4"/>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1690,7 +1868,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1699,50 +1877,61 @@
     <col min="5" max="5" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
-    <col min="8" max="8" width="9.75" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="11" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="12" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1762,10 +1951,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1774,13 +1963,22 @@
         <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1817,51 +2015,69 @@
       <c r="L3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="27" spans="1:12">
+      <c r="M3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>89</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1870,23 +2086,44 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:15">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -116,7 +116,7 @@
     <t>初始任务</t>
   </si>
   <si>
-    <t>100_01</t>
+    <t>100_s1</t>
   </si>
   <si>
     <t>gold,10|bundle_01,20</t>
@@ -180,9 +180,6 @@
     <t>出口列表</t>
   </si>
   <si>
-    <t>100_s1</t>
-  </si>
-  <si>
     <t>击杀刷新怪物</t>
   </si>
   <si>
@@ -196,6 +193,18 @@
   </si>
   <si>
     <t>100_s2_Main</t>
+  </si>
+  <si>
+    <t>101_s1</t>
+  </si>
+  <si>
+    <t>101_s1_Main</t>
+  </si>
+  <si>
+    <t>102_s1</t>
+  </si>
+  <si>
+    <t>102_s1_Main</t>
   </si>
   <si>
     <t>outcome_id</t>
@@ -1605,13 +1614,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
         <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1620,30 +1629,30 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1">
         <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1653,7 +1662,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>101</v>
@@ -1665,15 +1674,15 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>102</v>
@@ -1685,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1701,8 +1710,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="12.75" customWidth="1"/>
     <col min="3" max="3" width="25.625" customWidth="1"/>
@@ -1716,22 +1725,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1793,16 +1802,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
         <v>23</v>
@@ -1810,29 +1819,29 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
@@ -1840,24 +1849,33 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="E8" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1868,8 +1886,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="22.5" customWidth="1"/>
@@ -1889,46 +1907,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1951,10 +1969,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1963,10 +1981,10 @@
         <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s">
         <v>12</v>
@@ -2033,51 +2051,51 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -2086,21 +2104,21 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -2109,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2124,9 +2142,16 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -122,10 +122,13 @@
     <t>gold,10|bundle_01,20</t>
   </si>
   <si>
+    <t>CheckVariable,0,0,0,0,init.dialog_01,0</t>
+  </si>
+  <si>
     <t>初始任务2</t>
   </si>
   <si>
-    <t>101_01</t>
+    <t>101_s1</t>
   </si>
   <si>
     <t>TaskFinish,100,0,0,0,0,0</t>
@@ -134,7 +137,7 @@
     <t>初始任务3</t>
   </si>
   <si>
-    <t>102_01</t>
+    <t>102_s1</t>
   </si>
   <si>
     <t>TaskFinish,101,0,0,0,0,0</t>
@@ -195,15 +198,9 @@
     <t>100_s2_Main</t>
   </si>
   <si>
-    <t>101_s1</t>
-  </si>
-  <si>
     <t>101_s1_Main</t>
   </si>
   <si>
-    <t>102_s1</t>
-  </si>
-  <si>
     <t>102_s1_Main</t>
   </si>
   <si>
@@ -243,6 +240,9 @@
     <t>obj_id</t>
   </si>
   <si>
+    <t>custom_desc</t>
+  </si>
+  <si>
     <t>format_desc</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <t>自定义desc</t>
   </si>
   <si>
     <t>格式化描述</t>
@@ -1283,7 +1286,7 @@
     <col min="3" max="6" width="33.125" customWidth="1"/>
     <col min="7" max="7" width="17.875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1430,20 +1433,23 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="1">
         <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -1452,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1460,14 +1466,14 @@
         <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
@@ -1476,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1501,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1510,19 +1516,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1548,10 +1554,10 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1591,25 +1597,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1620,7 +1626,7 @@
         <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1629,30 +1635,30 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1">
         <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1662,7 +1668,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>101</v>
@@ -1682,7 +1688,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>102</v>
@@ -1694,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1725,22 +1731,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>61</v>
-      </c>
-      <c r="G1" t="s">
-        <v>62</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1755,7 +1761,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -1802,16 +1808,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
         <v>63</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>66</v>
       </c>
       <c r="H4" t="s">
         <v>23</v>
@@ -1819,29 +1825,29 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
@@ -1868,10 +1874,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="1" t="b">
         <v>1</v>
@@ -1886,108 +1892,111 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="4" width="29.625" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
-    <col min="10" max="12" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="2" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="5" width="29.625" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="17.25" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.375" customWidth="1"/>
+    <col min="11" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>75</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>81</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>84</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="L2" t="s">
         <v>84</v>
       </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s">
         <v>12</v>
@@ -1995,8 +2004,11 @@
       <c r="O2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -2042,8 +2054,11 @@
       <c r="O3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="27" spans="1:15">
+      <c r="P3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -2053,11 +2068,11 @@
       <c r="C4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
         <v>87</v>
@@ -2068,7 +2083,7 @@
       <c r="H4" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" t="s">
         <v>90</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -2086,72 +2101,80 @@
       <c r="N4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="B5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="B6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="G6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6">
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="M6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="B8" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
     <sheet name="quest_step_data" sheetId="2" r:id="rId2"/>
     <sheet name="quest_step_outcome" sheetId="4" r:id="rId3"/>
     <sheet name="quest_step_objective" sheetId="5" r:id="rId4"/>
+    <sheet name="quest_dialog_info" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="108">
   <si>
     <t>##var</t>
   </si>
@@ -343,6 +344,24 @@
   </si>
   <si>
     <t>initial_orc_02</t>
+  </si>
+  <si>
+    <t>quest_step_id</t>
+  </si>
+  <si>
+    <t>npc_id</t>
+  </si>
+  <si>
+    <t>dialog_id</t>
+  </si>
+  <si>
+    <t>任务step</t>
+  </si>
+  <si>
+    <t>绑定npc</t>
+  </si>
+  <si>
+    <t>quest101_s0_d0</t>
   </si>
 </sst>
 </file>
@@ -1500,6 +1519,8 @@
   <cols>
     <col min="4" max="4" width="33.875" customWidth="1"/>
     <col min="7" max="8" width="16.375" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2180,4 +2201,115 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="21.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>##var</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>CheckVariable,0,0,0,0,init.dialog_01,0</t>
+  </si>
+  <si>
+    <t>强盗？</t>
   </si>
   <si>
     <t>初始任务2</t>
@@ -1465,10 +1468,10 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -1477,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1485,14 +1488,14 @@
         <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
@@ -1501,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1528,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1537,19 +1540,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1575,10 +1578,10 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1618,25 +1621,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1647,7 +1650,7 @@
         <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1656,30 +1659,30 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1">
         <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1689,7 +1692,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>101</v>
@@ -1701,15 +1704,15 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>102</v>
@@ -1721,10 +1724,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1752,22 +1755,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1782,7 +1785,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -1829,16 +1832,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
         <v>23</v>
@@ -1846,29 +1849,29 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
@@ -1883,10 +1886,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="b">
         <v>1</v>
@@ -1895,10 +1898,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="b">
         <v>1</v>
@@ -1934,49 +1937,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2002,10 +2005,10 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
@@ -2014,10 +2017,10 @@
         <v>11</v>
       </c>
       <c r="L2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s">
         <v>12</v>
@@ -2087,55 +2090,55 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -2144,22 +2147,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -2168,13 +2171,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2185,17 +2188,23 @@
     </row>
     <row r="8" spans="1:16">
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
+      <c r="I8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1"/>
+      <c r="I9">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2221,13 +2230,13 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2272,13 +2281,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2286,11 +2295,11 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2298,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="25.125" customWidth="1" style="3" min="2" max="2"/>
@@ -1324,66 +1324,66 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
+      <c r="B8" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>采集草药</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>为镇长搜集草药并递交</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>200_s1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>gold,20</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>gold,20|quest_control_village01,1</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>采集木材</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>为木匠搜集木材并递交</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>201_s1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>gold,15</t>
         </is>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
@@ -1716,134 +1716,134 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>200_s1</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>搜集草药</t>
         </is>
       </c>
-      <c r="E10" t="b">
+      <c r="E10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="b">
+      <c r="F10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>200_s1_Main</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>200_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>200_s2</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>递交草药</t>
         </is>
       </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
+      <c r="E11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>200_s2_Main</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>200_s2_Main</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>201_s1</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>搜集木材</t>
         </is>
       </c>
-      <c r="E12" t="b">
+      <c r="E12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F12" t="b">
+      <c r="F12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>201_s1_Main</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>201_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>201_s2</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>递交木材</t>
         </is>
       </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
+      <c r="E13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>201_s2_Main</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>201_s2_Main</t>
         </is>
@@ -2109,84 +2109,84 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>200_s1_Main</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>200_s1_Main</t>
         </is>
       </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="E10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>200_s2</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>200_s2_Main</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>200_s2_Main</t>
         </is>
       </c>
-      <c r="E11" t="b">
+      <c r="E11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F11" t="b">
+      <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>201_s1_Main</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>201_s1_Main</t>
         </is>
       </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="E12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>201_s2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>201_s2_Main</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>201_s2_Main</t>
         </is>
       </c>
-      <c r="E13" t="b">
+      <c r="E13" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F13" t="b">
+      <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2646,194 +2646,194 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>200_s1_Main</t>
         </is>
       </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>搜集草药</t>
         </is>
       </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>OwnItem</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>200_s2_Main</t>
         </is>
       </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>递交草药</t>
         </is>
       </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>SubmitItem</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>201_s1_Main</t>
         </is>
       </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>搜集木材</t>
         </is>
       </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>OwnItem</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>201_s2_Main</t>
         </is>
       </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>递交木材</t>
         </is>
       </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>SubmitItem</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="quest_data" sheetId="1" r:id="rId1"/>
@@ -1352,13 +1352,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="25.125" style="1" customWidth="1"/>
     <col min="3" max="6" width="33.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="17.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="25.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1559,48 +1559,58 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8">
-        <v>200</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>42</v>
-      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9" spans="1:10">
       <c r="B9">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10">
         <v>201</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>44</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>45</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
         <v>46</v>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
         <v>47</v>
       </c>
     </row>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>TaskFinish,100,0,0,0,0,0</t>
+          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest_step_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest_step_outcome" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest_step_objective" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="quest_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="quest_step_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="quest_step_outcome" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="quest_step_objective" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.125" customWidth="1" style="1" min="2" max="2"/>
@@ -1226,7 +1226,6 @@
           <t>初始任务</t>
         </is>
       </c>
-      <c r="D5" s="0" t="n"/>
       <c r="E5" s="0" t="inlineStr">
         <is>
           <t>初始任务</t>
@@ -1260,7 +1259,6 @@
           <t>强盗？</t>
         </is>
       </c>
-      <c r="D6" s="0" t="n"/>
       <c r="E6" s="0" t="inlineStr">
         <is>
           <t>初始任务2</t>
@@ -1294,7 +1292,6 @@
           <t>初始任务3</t>
         </is>
       </c>
-      <c r="D7" s="0" t="n"/>
       <c r="E7" s="0" t="inlineStr">
         <is>
           <t>初始任务3</t>
@@ -1320,180 +1317,388 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="n"/>
-      <c r="C8" s="0" t="n"/>
-      <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="n"/>
-      <c r="F8" s="0" t="n"/>
-      <c r="G8" s="0" t="n"/>
-      <c r="H8" s="0" t="n"/>
-      <c r="I8" s="0" t="n"/>
+      <c r="B8" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>临时包扎</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>检查并稳定昏迷的卡莱尔</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>300_s1</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="n">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>采集草药</t>
+          <t>清理退路</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>为镇长搜集草药并递交</t>
+          <t>清掉附近怪物，确保能带卡莱尔离开</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>200_s1</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>gold,20|quest_control_village01,1</t>
+          <t>301_s1</t>
         </is>
       </c>
       <c r="H9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,300,0,0,0,0,0</t>
+        </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>home_elder</t>
+          <t>carlisle</t>
         </is>
       </c>
     </row>
     <row r="10" s="1">
       <c r="B10" s="0" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>采集木材</t>
+          <t>简易担架</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>为木匠搜集木材并递交</t>
+          <t>收集材料，带卡莱尔离开地牢</t>
         </is>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>201_s1</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>gold,15</t>
+          <t>302_s1</t>
         </is>
       </c>
       <c r="H10" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,301,0,0,0,0,0</t>
+        </is>
+      </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
     </row>
     <row r="11" s="1">
       <c r="B11" s="0" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>临时包扎</t>
+          <t>收复拼合村</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>检查并稳定昏迷的卡莱尔</t>
+          <t>击退占据 home_01 的流匪冒险者。</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>300_s1</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr"/>
+          <t>200_s1</t>
+        </is>
+      </c>
       <c r="H11" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>TaskFinish,302,0,0,0,0,0</t>
         </is>
       </c>
     </row>
     <row r="12" s="1">
       <c r="B12" s="0" t="n">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>清理退路</t>
+          <t>火堆盟约</t>
         </is>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>清掉附近怪物，确保能带卡莱尔离开</t>
+          <t>在火堆边确认村民与莉莉丝之间的最初信任。</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>301_s1</t>
-        </is>
-      </c>
-      <c r="G12" s="0" t="inlineStr"/>
+          <t>201_s1</t>
+        </is>
+      </c>
       <c r="H12" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>TaskFinish,300,0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>TaskFinish,200,0,0,0,0,0</t>
         </is>
       </c>
     </row>
     <row r="13" s="1">
       <c r="B13" s="0" t="n">
-        <v>302</v>
+        <v>202</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>简易担架</t>
+          <t>清点活人</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>收集材料，带卡莱尔离开地牢</t>
+          <t>埃蒙组织幸存者重新清点人手。</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>302_s1</t>
-        </is>
-      </c>
-      <c r="G13" s="0" t="inlineStr"/>
+          <t>202_s1</t>
+        </is>
+      </c>
       <c r="H13" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>TaskFinish,301,0,0,0,0,0</t>
+          <t>TaskFinish,201,0,0,0,0,0</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="n">
+        <v>203</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>锅不能灭</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>给负责食物与火堆的人补上燃料。</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>203_s1</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,202,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>保住灰露草</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>抢救灰露草棚里还能预处理的材料。</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>204_s1</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,203,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>干净一点再见人</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>整理临时住处、衣物和伤员清洁。</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>205_s1</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,204,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>夜路要有人看</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>补上村外路标与巡夜讯号。</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>206_s1</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,205,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>村东林缘调查</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>确认村东临时通路可以开放。</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>207_s1</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,206,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>带回雾线样本</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>从村东雾线边带回样本，确认继续深入森林的条件。</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>208_s1</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,207,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.875" customWidth="1" style="1" min="4" max="4"/>
@@ -1767,16 +1972,39 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="0" t="n"/>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1_Main</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1_Main</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>101_s1</t>
+          <t>102_s1</t>
         </is>
       </c>
       <c r="C8" s="0" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="0" t="b">
         <v>1</v>
@@ -1786,23 +2014,28 @@
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>101_s1_Main</t>
+          <t>102_s1_Main</t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>101_s1_Main</t>
+          <t>102_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>102_s1</t>
+          <t>300_s1</t>
         </is>
       </c>
       <c r="C9" s="0" t="n">
-        <v>102</v>
+        <v>300</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>搜集可用于包扎的草药</t>
+        </is>
       </c>
       <c r="E9" s="0" t="b">
         <v>1</v>
@@ -1812,94 +2045,94 @@
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t>102_s1_Main</t>
+          <t>300_s1_Main</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>102_s1_Main</t>
+          <t>300_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>200_s1</t>
+          <t>300_s2</t>
         </is>
       </c>
       <c r="C10" s="0" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>搜集草药</t>
+          <t>给卡莱尔临时包扎</t>
         </is>
       </c>
       <c r="E10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="0" t="b">
         <v>1</v>
       </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>200_s1_Main</t>
+          <t>300_s2_Main</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>200_s1_Main</t>
+          <t>300_s2_Main</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>200_s2</t>
+          <t>301_s1</t>
         </is>
       </c>
       <c r="C11" s="0" t="n">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>递交草药</t>
+          <t>清理附近残留怪物</t>
         </is>
       </c>
       <c r="E11" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>200_s2_Main</t>
+          <t>301_s1_Main</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>200_s2_Main</t>
+          <t>301_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>201_s1</t>
+          <t>302_s1</t>
         </is>
       </c>
       <c r="C12" s="0" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>搜集木材</t>
+          <t>搜集制作简易担架的材料</t>
         </is>
       </c>
       <c r="E12" s="0" t="b">
@@ -1910,27 +2143,27 @@
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>201_s1_Main</t>
+          <t>302_s1_Main</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>201_s1_Main</t>
+          <t>302_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="13" s="1">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>201_s2</t>
+          <t>302_s2</t>
         </is>
       </c>
       <c r="C13" s="0" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>递交木材</t>
+          <t>固定简易担架并唤醒卡莱尔</t>
         </is>
       </c>
       <c r="E13" s="0" t="b">
@@ -1941,32 +2174,32 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>201_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>201_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
     </row>
     <row r="14" s="1">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>300_s1</t>
+          <t>200_s1</t>
         </is>
       </c>
       <c r="C14" s="0" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>搜集可用于包扎的草药</t>
+          <t>击退占村流匪</t>
         </is>
       </c>
       <c r="E14" s="0" t="b">
@@ -1975,66 +2208,65 @@
       <c r="F14" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="0" t="n"/>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>300_s1_Main</t>
+          <t>200_s1_Main</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>300_s1_Main</t>
+          <t>200_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="15" s="1">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>300_s2</t>
+          <t>201_s1</t>
         </is>
       </c>
       <c r="C15" s="0" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>给卡莱尔临时包扎</t>
+          <t>火堆边的感谢与戒备</t>
         </is>
       </c>
       <c r="E15" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="0" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>201_s1_Main</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>201_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="16" s="1">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>301_s1</t>
+          <t>202_s1</t>
         </is>
       </c>
       <c r="C16" s="0" t="n">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>清理附近残留怪物</t>
+          <t>清点幸存者</t>
         </is>
       </c>
       <c r="E16" s="0" t="b">
@@ -2043,30 +2275,34 @@
       <c r="F16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="0" t="n"/>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>301_s1_Main</t>
+          <t>202_s1_Main</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>301_s1_Main</t>
+          <t>202_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="17" s="1">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>302_s1</t>
+          <t>203_s1</t>
         </is>
       </c>
       <c r="C17" s="0" t="n">
-        <v>302</v>
+        <v>203</v>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>搜集制作简易担架的材料</t>
+          <t>收集可烧的木料</t>
         </is>
       </c>
       <c r="E17" s="0" t="b">
@@ -2075,51 +2311,311 @@
       <c r="F17" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="0" t="n"/>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>302_s1_Main</t>
+          <t>203_s1_Main</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>302_s1_Main</t>
+          <t>203_s1_Main</t>
         </is>
       </c>
     </row>
     <row r="18" s="1">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>302_s2</t>
+          <t>203_s2</t>
         </is>
       </c>
       <c r="C18" s="0" t="n">
-        <v>302</v>
+        <v>203</v>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>固定简易担架并唤醒卡莱尔</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="b">
-        <v>0</v>
+          <t>交给管火堆的人</t>
+        </is>
       </c>
       <c r="F18" s="0" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>203_s2_Main</t>
         </is>
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>203_s2_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>收集能处理的灰露草</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1_Main</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>204</v>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>送到灰露棚预处理</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>205</v>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>整理临时住处</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>收集路标材料</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1_Main</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>206</v>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>交给巡夜的人安排</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>207</v>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>开放村东通路</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>带回雾线样本</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1_Main</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>交给埃蒙判断路线</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.75" customWidth="1" style="1" min="2" max="2"/>
@@ -2186,6 +2682,11 @@
           <t>finish_reward</t>
         </is>
       </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>set_variables</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -2224,6 +2725,11 @@
           <t>(map#sep=,|),string,int</t>
         </is>
       </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -2262,6 +2768,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -2299,6 +2810,11 @@
           <t>完成奖励</t>
         </is>
       </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>??????????</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -2316,8 +2832,6 @@
           <t>100_s1_Main</t>
         </is>
       </c>
-      <c r="E5" s="0" t="n"/>
-      <c r="F5" s="0" t="n"/>
       <c r="G5" s="0" t="inlineStr">
         <is>
           <t>100_s2</t>
@@ -2343,77 +2857,102 @@
       <c r="E6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="0" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="n"/>
-      <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="n"/>
-      <c r="F7" s="0" t="n"/>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1_Main</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1_Main</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>101_s1_Main</t>
+          <t>102_s1_Main</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>101_s1_Main</t>
+          <t>102_s1_Main</t>
         </is>
       </c>
       <c r="E8" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>102_s1_Main</t>
+          <t>300_s1_Main</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>300 s1 主跳转</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>102_s1_Main</t>
+          <t>300_s1_Main</t>
         </is>
       </c>
       <c r="E9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>300_s2</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>200_s1_Main</t>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>300 s2 完成</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>200_s1_Main</t>
+          <t>300_s2_Main</t>
         </is>
       </c>
       <c r="E10" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="0" t="b">
         <v>0</v>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>200_s2</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>200_s2_Main</t>
+          <t>301_s1_Main</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>301 s1 完成</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>200_s2_Main</t>
+          <t>301_s1_Main</t>
         </is>
       </c>
       <c r="E11" s="0" t="b">
@@ -2426,12 +2965,17 @@
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>201_s1_Main</t>
+          <t>302_s1_Main</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>302 s1 主跳转</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>201_s1_Main</t>
+          <t>302_s1_Main</t>
         </is>
       </c>
       <c r="E12" s="0" t="b">
@@ -2442,19 +2986,24 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>201_s2</t>
+          <t>302_s2</t>
         </is>
       </c>
     </row>
     <row r="13" s="1">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>201_s2_Main</t>
+          <t>302_s2_Main</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>302 s2 完成，后续切换卡莱尔苏醒状态</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>201_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="E13" s="0" t="b">
@@ -2467,135 +3016,315 @@
     <row r="14" s="1">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>300_s1_Main</t>
+          <t>200_s1_Main</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>300 s1 主跳转</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>300_s1_Main</t>
+          <t>200_s1_Main</t>
         </is>
       </c>
       <c r="E14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>300_s2</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>home_01.reclaimed</t>
+        </is>
+      </c>
     </row>
     <row r="15" s="1">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>201_s1_Main</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>300 s2 完成</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>201_s1_Main</t>
         </is>
       </c>
       <c r="E15" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="0" t="inlineStr"/>
-      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>home_01.fire_pact_done</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="1">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>301_s1_Main</t>
+          <t>202_s1_Main</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>301 s1 完成</t>
+          <t>???????</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>301_s1_Main</t>
+          <t>202_s1_Main</t>
         </is>
       </c>
       <c r="E16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr"/>
-      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>home_01.survivors_counted</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="1">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>302_s1_Main</t>
+          <t>203_s1_Main</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>302 s1 主跳转</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>302_s1_Main</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0" t="b">
-        <v>0</v>
+          <t>203_s1_Main</t>
+        </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>302_s2</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr"/>
+          <t>203_s2</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="1">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>203_s2_Main</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>302 s2 完成，后续切换卡莱尔苏醒状态</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>203_s2_Main</t>
         </is>
       </c>
       <c r="E18" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="0" t="inlineStr"/>
-      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>home_01.hearth_stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1_Main</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1_Main</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>204_s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>home_01.gray_dew_saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>home_01.cleaning_done</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1_Main</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1_Main</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>206_s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>home_01.watch_paths_marked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>home_01.east_unlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1_Main</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1_Main</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>208_s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>home_01.forest_route_unlocked</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2608,7 +3337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="1"/>
@@ -2964,7 +3693,6 @@
           <t>100_s1_Main</t>
         </is>
       </c>
-      <c r="C5" s="0" t="n"/>
       <c r="D5" s="0" t="inlineStr">
         <is>
           <t>击杀XX</t>
@@ -2996,7 +3724,6 @@
           <t>100_s2_Main</t>
         </is>
       </c>
-      <c r="C6" s="0" t="n"/>
       <c r="D6" s="0" t="inlineStr">
         <is>
           <t>击杀XX</t>
@@ -3023,20 +3750,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="n"/>
-      <c r="C7" s="0" t="n"/>
-      <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="n"/>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>101_s1_Main</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>101_s1_Main</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="n"/>
-      <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="n"/>
+          <t>102_s1_Main</t>
+        </is>
+      </c>
       <c r="I8" s="0" t="n">
         <v>1</v>
       </c>
@@ -3044,18 +3772,53 @@
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>102_s1_Main</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="n"/>
+          <t>300_s1_Main</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>搜集可用于包扎的草药</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
       <c r="I9" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>200_s1_Main</t>
+          <t>300_s2_Main</t>
         </is>
       </c>
       <c r="C10" s="0" t="b">
@@ -3063,7 +3826,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>搜集草药</t>
+          <t>给卡莱尔临时包扎</t>
         </is>
       </c>
       <c r="E10" s="0" t="b">
@@ -3074,11 +3837,11 @@
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>OwnItem</t>
+          <t>SubmitItem</t>
         </is>
       </c>
       <c r="I10" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="0" t="n">
         <v>0</v>
@@ -3095,13 +3858,18 @@
       <c r="N10" s="0" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>200_s2_Main</t>
+          <t>301_s1_Main</t>
         </is>
       </c>
       <c r="C11" s="0" t="b">
@@ -3109,7 +3877,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>递交草药</t>
+          <t>清理附近残留怪物</t>
         </is>
       </c>
       <c r="E11" s="0" t="b">
@@ -3120,11 +3888,11 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>SubmitItem</t>
+          <t>KillMonster</t>
         </is>
       </c>
       <c r="I11" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" s="0" t="n">
         <v>0</v>
@@ -3140,19 +3908,14 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t>quest_mat_herb</t>
-        </is>
-      </c>
-      <c r="O11" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
+          <t>initial_orc_01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>201_s1_Main</t>
+          <t>302_s1_Main</t>
         </is>
       </c>
       <c r="C12" s="0" t="b">
@@ -3160,7 +3923,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>搜集木材</t>
+          <t>搜集制作简易担架的材料</t>
         </is>
       </c>
       <c r="E12" s="0" t="b">
@@ -3198,7 +3961,7 @@
     <row r="13" s="1">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>201_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="C13" s="0" t="b">
@@ -3206,7 +3969,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>递交木材</t>
+          <t>固定简易担架并唤醒卡莱尔</t>
         </is>
       </c>
       <c r="E13" s="0" t="b">
@@ -3242,22 +4005,19 @@
       </c>
       <c r="O13" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
     </row>
     <row r="14" s="1">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>300_s1_Main</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="b">
-        <v>0</v>
+          <t>200_s1_Main</t>
+        </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>搜集可用于包扎的草药</t>
+          <t>击退占据村子的流匪冒险者</t>
         </is>
       </c>
       <c r="E14" s="0" t="b">
@@ -3268,43 +4028,27 @@
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>OwnItem</t>
+          <t>KillMonster</t>
         </is>
       </c>
       <c r="I14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t>quest_mat_herb</t>
-        </is>
-      </c>
-      <c r="O14" s="0" t="n"/>
+          <t>home_robber_n</t>
+        </is>
+      </c>
     </row>
     <row r="15" s="1">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="b">
-        <v>0</v>
+          <t>201_s1_Main</t>
+        </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>给卡莱尔临时包扎</t>
+          <t>和埃蒙在火堆边谈谈</t>
         </is>
       </c>
       <c r="E15" s="0" t="b">
@@ -3315,47 +4059,27 @@
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>SubmitItem</t>
+          <t>Talk</t>
         </is>
       </c>
       <c r="I15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="0" t="inlineStr">
-        <is>
-          <t>quest_mat_herb</t>
-        </is>
-      </c>
       <c r="O15" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
     </row>
     <row r="16" s="1">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>301_s1_Main</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="b">
-        <v>0</v>
+          <t>202_s1_Main</t>
+        </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>清理附近残留怪物</t>
+          <t>向埃蒙确认幸存者清点</t>
         </is>
       </c>
       <c r="E16" s="0" t="b">
@@ -3366,43 +4090,27 @@
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>KillMonster</t>
+          <t>Talk</t>
         </is>
       </c>
       <c r="I16" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="0" t="inlineStr">
-        <is>
-          <t>initial_orc_01</t>
-        </is>
-      </c>
-      <c r="O16" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="1">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>302_s1_Main</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="b">
-        <v>0</v>
+          <t>203_s1_Main</t>
+        </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>搜集制作简易担架的材料</t>
+          <t>收集可用木料</t>
         </is>
       </c>
       <c r="E17" s="0" t="b">
@@ -3419,37 +4127,21 @@
       <c r="I17" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" s="0" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
-      <c r="O17" s="0" t="n"/>
     </row>
     <row r="18" s="1">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="b">
-        <v>0</v>
+          <t>203_s2_Main</t>
+        </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>固定简易担架并唤醒卡莱尔</t>
+          <t>把木料交给管火堆的人</t>
         </is>
       </c>
       <c r="E18" s="0" t="b">
@@ -3466,18 +4158,6 @@
       <c r="I18" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" s="0" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
@@ -3485,7 +4165,270 @@
       </c>
       <c r="O18" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>204_s1_Main</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>收集能抢救的灰露草</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>把灰露草送去预处理</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>SubmitItem</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
+      </c>
+      <c r="O20" s="0" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>向埃蒙确认临时住处已整理</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>206_s1_Main</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>收集路标和讯号材料</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>把材料交给安排巡夜的人</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>SubmitItem</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_wood</t>
+        </is>
+      </c>
+      <c r="O23" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>请埃蒙开放村东通路</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>208_s1_Main</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>取得雾线边的样本</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>把雾线样本交给埃蒙</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>SubmitItem</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="0" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
+      </c>
+      <c r="O26" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/quests.xlsx
+++ b/Config/Datas/quests.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.125" customWidth="1" style="1" min="2" max="2"/>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="1">
       <c r="B19" s="0" t="n">
         <v>208</v>
       </c>
@@ -1697,6 +1697,150 @@
         </is>
       </c>
       <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="1">
+      <c r="B20" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>林缘立足</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>清理森林入口附近的魔物，确认一条可靠的退路。</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>209_s1</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>berry,2</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,208,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n"/>
+    </row>
+    <row r="21" s="1">
+      <c r="B21" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>不属于森林的脚印</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>调查林中的人类活动痕迹，并击退盘踞在中段的偷猎者。</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>210_s1</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>gold,20</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,209,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n"/>
+    </row>
+    <row r="22" s="1">
+      <c r="B22" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>北路花露</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>从森林北路取得两份森林花露，并带回村庄交给埃蒙判断。</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>211_s1</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>gold,15</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,210,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="1">
+      <c r="B23" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>心木回声</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>触碰森林之心，确认它对主角的反应后向埃蒙汇报。</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>212_s1</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>gold,30</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,211,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
@@ -1714,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.875" customWidth="1" style="1" min="4" max="4"/>
@@ -2586,7 +2730,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="1">
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>208_s2</t>
@@ -2616,6 +2760,206 @@
       <c r="I26" s="0" t="inlineStr">
         <is>
           <t>208_s2_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="1">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>清理森林入口</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="n"/>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1_Main</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="1">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>210</v>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>击退森林偷猎者</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="n"/>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1_Main</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="1">
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>取得两份森林花露</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="n"/>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1_Main</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" s="1">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>把森林花露交给埃蒙</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="1">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>聆听森林之心</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="n"/>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1_Main</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1_Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="1">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>向埃蒙汇报森林之心的反应</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.75" customWidth="1" style="1" min="2" max="2"/>
@@ -3301,7 +3645,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="1">
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>208_s2_Main</t>
@@ -3323,6 +3667,176 @@
       <c r="I26" s="0" t="inlineStr">
         <is>
           <t>home_01.forest_route_unlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="1">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1_Main</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>入口据点确认</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1_Main</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>forest_01.foothold_secured</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" s="1">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1_Main</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>偷猎者被逐退</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1_Main</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>forest_01.poachers_driven_off</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" s="1">
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1_Main</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>取得花露</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1_Main</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>211_s2</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n"/>
+    </row>
+    <row r="30" s="1">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>交付花露</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>forest_01.dew_sample_delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="1">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1_Main</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>聆听森林之心</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1_Main</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>212_s2</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="n"/>
+    </row>
+    <row r="32" s="1">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>完成森林之心汇报</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>forest_01.heart_reported</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="1" max="1"/>
@@ -4396,7 +4910,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="1">
       <c r="B26" s="0" t="inlineStr">
         <is>
           <t>208_s2_Main</t>
@@ -4427,6 +4941,296 @@
         </is>
       </c>
       <c r="O26" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="1">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>209_s1_Main</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>击败入口附近的绿色史莱姆</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="0" t="inlineStr">
+        <is>
+          <t>slime_green</t>
+        </is>
+      </c>
+      <c r="O27" s="0" t="n"/>
+    </row>
+    <row r="28" s="1">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>210_s1_Main</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>击退森林中的偷猎者</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="0" t="inlineStr">
+        <is>
+          <t>home_robber_n</t>
+        </is>
+      </c>
+      <c r="O28" s="0" t="n"/>
+    </row>
+    <row r="29" s="1">
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>211_s1_Main</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="inlineStr">
+        <is>
+          <t>取得森林花露</t>
+        </is>
+      </c>
+      <c r="E29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="0" t="inlineStr">
+        <is>
+          <t>mat_forest_dew</t>
+        </is>
+      </c>
+      <c r="O29" s="0" t="n"/>
+    </row>
+    <row r="30" s="1">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="0" t="inlineStr">
+        <is>
+          <t>把森林花露交给埃蒙</t>
+        </is>
+      </c>
+      <c r="E30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>SubmitItem</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="0" t="inlineStr">
+        <is>
+          <t>mat_forest_dew</t>
+        </is>
+      </c>
+      <c r="O30" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="1">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>212_s1_Main</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>聆听森林之心</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>InteractEntity</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
+        <is>
+          <t>forest_heart_altar</t>
+        </is>
+      </c>
+      <c r="O31" s="0" t="inlineStr">
+        <is>
+          <t>forest_heart_altar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" s="1">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>向埃蒙汇报</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="0" t="n"/>
+      <c r="O32" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
